--- a/artfynd/A 60057-2023 artfynd.xlsx
+++ b/artfynd/A 60057-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60057-2023 artfynd.xlsx
+++ b/artfynd/A 60057-2023 artfynd.xlsx
@@ -1519,7 +1519,7 @@
         <v>123660350</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 60057-2023 artfynd.xlsx
+++ b/artfynd/A 60057-2023 artfynd.xlsx
@@ -1519,7 +1519,7 @@
         <v>123660350</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 60057-2023 artfynd.xlsx
+++ b/artfynd/A 60057-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1403,231 +1403,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>115533192</v>
-      </c>
-      <c r="B8" t="n">
-        <v>103146</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Kungstorp, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>669113</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6556202</v>
-      </c>
-      <c r="S8" t="n">
-        <v>50</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Nynäshamn</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sorunda</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Ingela Fredriksson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Ingela Fredriksson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>123660350</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57895</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>103037</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Stare</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Sturnus vulgaris</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Kungstorp, Srm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>669113</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6556202</v>
-      </c>
-      <c r="S9" t="n">
-        <v>50</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Nynäshamn</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Sorunda</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Ingela Fredriksson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Ingela Fredriksson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60057-2023 artfynd.xlsx
+++ b/artfynd/A 60057-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70810835</v>
+        <v>85519243</v>
       </c>
       <c r="B2" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -720,16 +715,17 @@
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kungstorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669113.4880637776</v>
+        <v>669113</v>
       </c>
       <c r="R2" t="n">
-        <v>6556202.379603144</v>
+        <v>6556202</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76853071</v>
+        <v>93317734</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,31 +795,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669113.4880637776</v>
+        <v>669113</v>
       </c>
       <c r="R3" t="n">
-        <v>6556202.379603144</v>
+        <v>6556202</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -876,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-04-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-04-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,49 +893,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>77186407</v>
+        <v>94062636</v>
       </c>
       <c r="B4" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>102626</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -971,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669113.4880637776</v>
+        <v>669113</v>
       </c>
       <c r="R4" t="n">
-        <v>6556202.379603144</v>
+        <v>6556202</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>93317734</v>
+        <v>101301833</v>
       </c>
       <c r="B5" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,33 +1013,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>102980</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1095,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>669113.4880637776</v>
+        <v>669113</v>
       </c>
       <c r="R5" t="n">
-        <v>6556202.379603144</v>
+        <v>6556202</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1125,22 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,12 +1114,7 @@
         <v>99276074</v>
       </c>
       <c r="B6" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>669113.4880637776</v>
+        <v>669113</v>
       </c>
       <c r="R6" t="n">
-        <v>6556202.379603144</v>
+        <v>6556202</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1252,19 +1191,9 @@
           <t>2022-03-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,49 +1220,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115173872</v>
+        <v>77186407</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103042</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1373,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,6 +1326,329 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70810835</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kungstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>669113</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6556202</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-04-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ingela Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ingela Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115173872</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kungstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>669113</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6556202</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ingela Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ingela Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>76853071</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kungstorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>669113</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6556202</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-04-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-04-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ingela Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ingela Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60057-2023 artfynd.xlsx
+++ b/artfynd/A 60057-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85519243</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93317734</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94062636</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101301833</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99276074</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77186407</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70810835</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173872</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,8 +1694,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76853071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>